--- a/salidas/tabla_calviv_cso_pond.xlsx
+++ b/salidas/tabla_calviv_cso_pond.xlsx
@@ -17,19 +17,19 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">Clase directivo-profesional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clase media rutinaria</t>
+    <t xml:space="preserve">Directiva-profesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media rutinaria</t>
   </si>
   <si>
     <t xml:space="preserve">Pequeña burguesía</t>
   </si>
   <si>
-    <t xml:space="preserve">Clase obrera calificada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clase obrera no calificada</t>
+    <t xml:space="preserve">Obrera calificada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obrera no calificada</t>
   </si>
   <si>
     <t xml:space="preserve">aceptable</t>
@@ -395,19 +395,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>859.847964615019</v>
+        <v>616805</v>
       </c>
       <c r="C2" t="n">
-        <v>1484.6808927818</v>
+        <v>834897</v>
       </c>
       <c r="D2" t="n">
-        <v>434.788961821768</v>
+        <v>277722</v>
       </c>
       <c r="E2" t="n">
-        <v>829.822087260838</v>
+        <v>831295</v>
       </c>
       <c r="F2" t="n">
-        <v>536.774491778275</v>
+        <v>366173</v>
       </c>
     </row>
     <row r="3">
@@ -415,19 +415,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>43.1325236136574</v>
+        <v>30810</v>
       </c>
       <c r="C3" t="n">
-        <v>200.834015292699</v>
+        <v>170765</v>
       </c>
       <c r="D3" t="n">
-        <v>59.5175186091668</v>
+        <v>21744</v>
       </c>
       <c r="E3" t="n">
-        <v>213.501178326754</v>
+        <v>232528</v>
       </c>
       <c r="F3" t="n">
-        <v>208.417030775575</v>
+        <v>104121</v>
       </c>
     </row>
     <row r="4">
@@ -438,16 +438,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1.69736815113439</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.179902330058231</v>
+        <v>3591</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0931485415258</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8.34346476527668</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="5">
